--- a/docs/заказы-купер/реестр-перевыставление-Фурик.xlsx
+++ b/docs/заказы-купер/реестр-перевыставление-Фурик.xlsx
@@ -11,7 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Правила" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Реестр Фурик'!$A$1:$F$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Реестр Фурик'!$A$13:$G$53</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Реестр Фурик'!$13:$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,8 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="DD.MM.YYYY"/>
+  </numFmts>
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,28 +33,38 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial Black"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="00000000"/>
+      <sz val="16"/>
     </font>
     <font>
-      <b val="1"/>
+      <name val="Arial"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Arial Black"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="00000000"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <color rgb="00333333"/>
-      <sz val="11"/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="001A1A1A"/>
-      <sz val="11"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="6">
@@ -62,26 +76,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001A1A1A"/>
+        <fgColor rgb="00FFF2C2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C00000"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF0F0"/>
+        <fgColor rgb="00FFF8E7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F5F5F5"/>
+        <fgColor rgb="00FFF0C8"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -90,61 +104,193 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color rgb="00D4B552"/>
+      </left>
+      <right style="medium">
+        <color rgb="00D4B552"/>
+      </right>
+      <top style="medium">
+        <color rgb="00D4B552"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00D4B552"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00D4B552"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00D4B552"/>
+      </right>
+      <top style="medium">
+        <color rgb="00D4B552"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00D4B552"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00D4B552"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00D4B552"/>
+      </right>
+      <top style="medium">
+        <color rgb="00D4B552"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00D4B552"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00E5DDD2"/>
       </left>
       <right style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00E5DDD2"/>
       </right>
       <top style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00E5DDD2"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="00E5DDD2"/>
       </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E5DDD2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E5DDD2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E5DDD2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E5DDD2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E5DDD2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E5DDD2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E5DDD2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E5DDD2"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="5" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -508,1313 +654,1368 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>Дата заказа</t>
-        </is>
-      </c>
-      <c r="B1" s="7" t="inlineStr">
-        <is>
-          <t>№ заказа</t>
-        </is>
-      </c>
-      <c r="C1" s="7" t="inlineStr">
-        <is>
-          <t>Позиция</t>
-        </is>
-      </c>
-      <c r="D1" s="7" t="inlineStr">
-        <is>
-          <t>Кол-во</t>
-        </is>
-      </c>
-      <c r="E1" s="7" t="inlineStr">
-        <is>
-          <t>Стоимость</t>
-        </is>
-      </c>
-      <c r="F1" s="7" t="inlineStr">
-        <is>
-          <t>Сумма</t>
-        </is>
-      </c>
-      <c r="G1" s="7" t="inlineStr">
-        <is>
-          <t>Источник</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>2026-01-29</t>
-        </is>
-      </c>
-      <c r="B2" s="15" t="inlineStr">
-        <is>
-          <t>H94498947135</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>Кетчуп Махеевъ Шашлычный 500 г</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="9" t="n">
-        <v>114.99</v>
-      </c>
-      <c r="F2" s="9" t="n">
-        <v>114.99</v>
-      </c>
-      <c r="G2" s="8" t="inlineStr">
-        <is>
-          <t>Гипер Лента / Купер</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
-      <c r="B3" s="16" t="inlineStr">
-        <is>
-          <t>H96565079374</t>
-        </is>
-      </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>Карамель леденцовая HALLS Colors ассорти 25 г</t>
-        </is>
-      </c>
-      <c r="D3" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="11" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="G3" s="10" t="inlineStr">
-        <is>
-          <t>METRO / Купер</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>H96565079374</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Кетчуп Махеевъ Шашлычный 500 г</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>130</v>
-      </c>
-      <c r="F4" s="9" t="n">
-        <v>130</v>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>METRO / Купер</t>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>РЕЕСТР ЛИЧНЫХ ПОКУПОК · СБЕРМАРКЕТ → ФУРКАТЖОН</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>К перевыставлению  ·  40 позиций  ·  28 заказов  ·  27.09.2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Согласованные личные позиции из заказов доставки. Товары кофейни и сервисные сборы не включены.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>H96565079374</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>Леденцы Halls Ментол экстра 25 г</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>METRO / Купер</t>
-        </is>
-      </c>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Поле</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>H46412399379</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Гель Persil Premium Color для стирки цветного белья 1,76 л</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>669.99</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>669.99</v>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>Ашан / Купер</t>
-        </is>
-      </c>
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Кому</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Фуркатжон (перевыставление личных покупок)</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>H04543322490</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>Кетчуп Махеевъ Шашлычный 500 г</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>126</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>126</v>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>METRO / Купер</t>
-        </is>
-      </c>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Сбермаркет / Купер</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="n"/>
+      <c r="D7" s="12" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>H83535345846</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Кетчуп Махеевъ Шашлычный 500 г</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>131</v>
-      </c>
-      <c r="F8" s="9" t="n">
-        <v>131</v>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>METRO / Купер</t>
-        </is>
-      </c>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Позиций</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+          <t>Заказов</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="12" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Итого</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>9 853,56 ₽</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Дата заказа</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>№ заказа</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Позиция</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Кол-во</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Стоимость</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Сумма</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="13" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>H94498947135</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Кетчуп Махеевъ Шашлычный 500 г</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>114.99</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>114.99</v>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>Гипер Лента / Купер</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="18" t="n">
+        <v>46071</v>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>H96565079374</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Карамель леденцовая HALLS Colors ассорти 25 г</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="21" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="F15" s="22" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>METRO / Купер</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="13" t="n">
+        <v>46071</v>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>H96565079374</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Кетчуп Махеевъ Шашлычный 500 г</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>130</v>
+      </c>
+      <c r="F16" s="17" t="n">
+        <v>130</v>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>METRO / Купер</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="18" t="n">
+        <v>46071</v>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>H96565079374</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Леденцы Halls Ментол экстра 25 г</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="21" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="F17" s="22" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>METRO / Купер</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="13" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>H46412399379</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Гель Persil Premium Color для стирки цветного белья 1,76 л</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="16" t="n">
+        <v>669.99</v>
+      </c>
+      <c r="F18" s="17" t="n">
+        <v>669.99</v>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>Ашан / Купер</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="18" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>H04543322490</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Кетчуп Махеевъ Шашлычный 500 г</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="21" t="n">
+        <v>126</v>
+      </c>
+      <c r="F19" s="22" t="n">
+        <v>126</v>
+      </c>
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>METRO / Купер</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="13" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>H83535345846</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Кетчуп Махеевъ Шашлычный 500 г</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>131</v>
+      </c>
+      <c r="F20" s="17" t="n">
+        <v>131</v>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>METRO / Купер</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="18" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>H87785389118</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>Кетчуп Махеевъ Шашлычный 500 г</t>
         </is>
       </c>
-      <c r="D9" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="11" t="n">
+      <c r="D21" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="21" t="n">
         <v>132</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F21" s="22" t="n">
         <v>132</v>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G21" s="11" t="inlineStr">
         <is>
           <t>METRO / Купер</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="inlineStr">
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="13" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>H49378154466</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>Кетчуп Махеевъ Шашлычный 500 г</t>
         </is>
       </c>
-      <c r="D10" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="9" t="n">
+      <c r="D22" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="16" t="n">
         <v>109.99</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F22" s="17" t="n">
         <v>109.99</v>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t>О'КЕЙ / Купер</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="18" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>H71721563731</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>Зубная паста Biorepair Scudo Attivo 75 мл</t>
         </is>
       </c>
-      <c r="D11" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="11" t="n">
+      <c r="D23" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="21" t="n">
         <v>799</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F23" s="22" t="n">
         <v>799</v>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G23" s="11" t="inlineStr">
         <is>
           <t>METRO / Купер</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="13" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>H71721563731</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>Кетчуп Махеевъ Шашлычный 500 г</t>
         </is>
       </c>
-      <c r="D12" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="9" t="n">
+      <c r="D24" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="16" t="n">
         <v>140</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F24" s="17" t="n">
         <v>140</v>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>METRO / Купер</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="18" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B25" s="19" t="inlineStr">
         <is>
           <t>H29699583853</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>Кетчуп Балтимор Татарский ГОСТ 260 г</t>
         </is>
       </c>
-      <c r="D13" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="11" t="n">
+      <c r="D25" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="21" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="F13" s="11" t="n">
+      <c r="F25" s="22" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G25" s="11" t="inlineStr">
         <is>
           <t>METRO / Купер</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="13" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>H29699583853</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>Кетчуп Махеевъ Томатный 300 г</t>
         </is>
       </c>
-      <c r="D14" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="9" t="n">
+      <c r="D26" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="16" t="n">
         <v>92.90000000000001</v>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="F26" s="17" t="n">
         <v>92.90000000000001</v>
       </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>METRO / Купер</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="18" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B27" s="19" t="inlineStr">
         <is>
           <t>H29699583853</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C27" s="11" t="inlineStr">
         <is>
           <t>Освежитель воздуха Glade Нежность полевых цветов 300 мл</t>
         </is>
       </c>
-      <c r="D15" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="11" t="n">
+      <c r="D27" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="21" t="n">
         <v>169</v>
       </c>
-      <c r="F15" s="11" t="n">
+      <c r="F27" s="22" t="n">
         <v>169</v>
       </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="G27" s="11" t="inlineStr">
         <is>
           <t>METRO / Купер</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="13" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>H29699583853</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>Освежитель воздуха Glade После дождя 300 мл</t>
         </is>
       </c>
-      <c r="D16" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="9" t="n">
+      <c r="D28" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="16" t="n">
         <v>169</v>
       </c>
-      <c r="F16" s="9" t="n">
+      <c r="F28" s="17" t="n">
         <v>169</v>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr">
         <is>
           <t>METRO / Купер</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="18" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B29" s="19" t="inlineStr">
         <is>
           <t>H39496308892</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C29" s="11" t="inlineStr">
         <is>
           <t>Кетчуп Махеевъ Шашлычный 500 г</t>
         </is>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D29" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E29" s="21" t="n">
         <v>119.99</v>
       </c>
-      <c r="F17" s="11" t="n">
+      <c r="F29" s="22" t="n">
         <v>239.98</v>
       </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="G29" s="11" t="inlineStr">
         <is>
           <t>Гипер Лента / Купер</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="inlineStr">
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="13" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>H92170137339</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>Гель Ласка Восстановление Color для стирки цветного белья 3 л</t>
         </is>
       </c>
-      <c r="D18" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="9" t="n">
+      <c r="D30" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="16" t="n">
         <v>731.99</v>
       </c>
-      <c r="F18" s="9" t="n">
+      <c r="F30" s="17" t="n">
         <v>731.99</v>
       </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="G30" s="8" t="inlineStr">
         <is>
           <t>Гипер Лента / Купер</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="18" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B31" s="19" t="inlineStr">
         <is>
           <t>H46192300566</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>Кетчуп Махеевъ Шашлычный 500 г</t>
         </is>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D31" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E31" s="21" t="n">
         <v>188.67</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F31" s="22" t="n">
         <v>377.34</v>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G31" s="11" t="inlineStr">
         <is>
           <t>О'КЕЙ / Купер</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="inlineStr">
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="13" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>H59259199970</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>Кетчуп Heinz Томатный 460 г</t>
         </is>
       </c>
-      <c r="D20" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="9" t="n">
+      <c r="D32" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="16" t="n">
         <v>236</v>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F32" s="17" t="n">
         <v>236</v>
       </c>
-      <c r="G20" s="8" t="inlineStr">
+      <c r="G32" s="8" t="inlineStr">
         <is>
           <t>METRO / Купер</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="18" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B33" s="19" t="inlineStr">
         <is>
           <t>H87091038718</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>Кетчуп Махеевъ Томатный 300 г</t>
         </is>
       </c>
-      <c r="D21" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="11" t="n">
+      <c r="D33" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="21" t="n">
         <v>105.99</v>
       </c>
-      <c r="F21" s="11" t="n">
+      <c r="F33" s="22" t="n">
         <v>105.99</v>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="G33" s="11" t="inlineStr">
         <is>
           <t>О'КЕЙ / Купер</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="13" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>H87091038718</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>Кетчуп Махеевъ Шашлычный 300 г</t>
         </is>
       </c>
-      <c r="D22" s="8" t="n">
+      <c r="D34" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E34" s="16" t="n">
         <v>105.99</v>
       </c>
-      <c r="F22" s="9" t="n">
+      <c r="F34" s="17" t="n">
         <v>317.97</v>
       </c>
-      <c r="G22" s="8" t="inlineStr">
+      <c r="G34" s="8" t="inlineStr">
         <is>
           <t>О'КЕЙ / Купер</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="18" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
         <is>
           <t>H70717316845</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C35" s="11" t="inlineStr">
         <is>
           <t>Кетчуп Махеевъ Шашлычный 500 г</t>
         </is>
       </c>
-      <c r="D23" s="10" t="n">
+      <c r="D35" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="E23" s="11" t="n">
+      <c r="E35" s="21" t="n">
         <v>119</v>
       </c>
-      <c r="F23" s="11" t="n">
+      <c r="F35" s="22" t="n">
         <v>238</v>
       </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="G35" s="11" t="inlineStr">
         <is>
           <t>Магнит / Купер</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="B24" s="15" t="inlineStr">
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="13" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t>H79418444932</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>Кетчуп Махеевъ Шашлычный 300 г</t>
         </is>
       </c>
-      <c r="D24" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="9" t="n">
+      <c r="D36" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="16" t="n">
         <v>76.98999999999999</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F36" s="17" t="n">
         <v>76.98999999999999</v>
       </c>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="G36" s="8" t="inlineStr">
         <is>
           <t>Globus / Купер</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="18" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B37" s="19" t="inlineStr">
         <is>
           <t>H79418444932</t>
         </is>
       </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>Кетчуп Махеевъ Шашлычный 500 г</t>
         </is>
       </c>
-      <c r="D25" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="11" t="n">
+      <c r="D37" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="21" t="n">
         <v>168.99</v>
       </c>
-      <c r="F25" s="11" t="n">
+      <c r="F37" s="22" t="n">
         <v>168.99</v>
       </c>
-      <c r="G25" s="10" t="inlineStr">
+      <c r="G37" s="11" t="inlineStr">
         <is>
           <t>Globus / Купер</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="B26" s="15" t="inlineStr">
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="13" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>H67744686409</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>Зубная паста Biorepair Scudo Attivo 75 мл</t>
         </is>
       </c>
-      <c r="D26" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="9" t="n">
+      <c r="D38" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="16" t="n">
         <v>749.99</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F38" s="17" t="n">
         <v>749.99</v>
       </c>
-      <c r="G26" s="8" t="inlineStr">
+      <c r="G38" s="8" t="inlineStr">
         <is>
           <t>Globus / Купер</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="18" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B39" s="19" t="inlineStr">
         <is>
           <t>H76795852777</t>
         </is>
       </c>
-      <c r="C27" s="10" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>Кетчуп Махеевъ Шашлычный 500 г</t>
         </is>
       </c>
-      <c r="D27" s="10" t="n">
+      <c r="D39" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="E27" s="11" t="n">
+      <c r="E39" s="21" t="n">
         <v>139.99</v>
       </c>
-      <c r="F27" s="11" t="n">
+      <c r="F39" s="22" t="n">
         <v>279.98</v>
       </c>
-      <c r="G27" s="10" t="inlineStr">
+      <c r="G39" s="11" t="inlineStr">
         <is>
           <t>Перекрёсток / Купер</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="B28" s="15" t="inlineStr">
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="13" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
         <is>
           <t>H45301503055</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C40" s="8" t="inlineStr">
         <is>
           <t>Кетчуп Махеевъ Шашлычный 500 г</t>
         </is>
       </c>
-      <c r="D28" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="9" t="n">
+      <c r="D40" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="16" t="n">
         <v>120</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F40" s="17" t="n">
         <v>120</v>
       </c>
-      <c r="G28" s="8" t="inlineStr">
+      <c r="G40" s="8" t="inlineStr">
         <is>
           <t>METRO / Купер</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="18" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B41" s="19" t="inlineStr">
         <is>
           <t>H33011600833</t>
         </is>
       </c>
-      <c r="C29" s="10" t="inlineStr">
+      <c r="C41" s="11" t="inlineStr">
         <is>
           <t>Аджика Амца Абхазская классическая 200 г</t>
         </is>
       </c>
-      <c r="D29" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="11" t="n">
+      <c r="D41" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="21" t="n">
         <v>239.99</v>
       </c>
-      <c r="F29" s="11" t="n">
+      <c r="F41" s="22" t="n">
         <v>239.99</v>
       </c>
-      <c r="G29" s="10" t="inlineStr">
+      <c r="G41" s="11" t="inlineStr">
         <is>
           <t>Пятёрочка / Купер</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B30" s="15" t="inlineStr">
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="13" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B42" s="14" t="inlineStr">
         <is>
           <t>H33011600833</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>Соус Astoria Бургер для бутербродов и закусок 200 г</t>
         </is>
       </c>
-      <c r="D30" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="9" t="n">
+      <c r="D42" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="16" t="n">
         <v>88.98999999999999</v>
       </c>
-      <c r="F30" s="9" t="n">
+      <c r="F42" s="17" t="n">
         <v>88.98999999999999</v>
       </c>
-      <c r="G30" s="8" t="inlineStr">
+      <c r="G42" s="8" t="inlineStr">
         <is>
           <t>Пятёрочка / Купер</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="18" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B43" s="19" t="inlineStr">
         <is>
           <t>H76983734926</t>
         </is>
       </c>
-      <c r="C31" s="10" t="inlineStr">
+      <c r="C43" s="11" t="inlineStr">
         <is>
           <t>Кетчуп Махеевъ Томатный 300 г</t>
         </is>
       </c>
-      <c r="D31" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="11" t="n">
+      <c r="D43" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" s="21" t="n">
         <v>94.98999999999999</v>
       </c>
-      <c r="F31" s="11" t="n">
+      <c r="F43" s="22" t="n">
         <v>94.98999999999999</v>
       </c>
-      <c r="G31" s="10" t="inlineStr">
+      <c r="G43" s="11" t="inlineStr">
         <is>
           <t>Пятёрочка / Купер</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="13" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B44" s="14" t="inlineStr">
         <is>
           <t>H88971019492</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>Аджика Амца Абхазская классическая 200 г</t>
         </is>
       </c>
-      <c r="D32" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="9" t="n">
+      <c r="D44" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="16" t="n">
         <v>239.99</v>
       </c>
-      <c r="F32" s="9" t="n">
+      <c r="F44" s="17" t="n">
         <v>239.99</v>
       </c>
-      <c r="G32" s="8" t="inlineStr">
+      <c r="G44" s="8" t="inlineStr">
         <is>
           <t>Пятёрочка / Купер</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="18" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B45" s="19" t="inlineStr">
         <is>
           <t>H98782441555</t>
         </is>
       </c>
-      <c r="C33" s="10" t="inlineStr">
+      <c r="C45" s="11" t="inlineStr">
         <is>
           <t>Кетчуп Махеевъ Томатный 300 г</t>
         </is>
       </c>
-      <c r="D33" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="11" t="n">
+      <c r="D45" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="21" t="n">
         <v>94.98999999999999</v>
       </c>
-      <c r="F33" s="11" t="n">
+      <c r="F45" s="22" t="n">
         <v>94.98999999999999</v>
       </c>
-      <c r="G33" s="10" t="inlineStr">
+      <c r="G45" s="11" t="inlineStr">
         <is>
           <t>Пятёрочка / Купер</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B34" s="15" t="inlineStr">
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="13" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
         <is>
           <t>H78873793353</t>
         </is>
       </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>Аджика Амца Абхазская классическая 200 г</t>
         </is>
       </c>
-      <c r="D34" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="9" t="n">
+      <c r="D46" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="16" t="n">
         <v>239.99</v>
       </c>
-      <c r="F34" s="9" t="n">
+      <c r="F46" s="17" t="n">
         <v>239.99</v>
       </c>
-      <c r="G34" s="8" t="inlineStr">
+      <c r="G46" s="8" t="inlineStr">
         <is>
           <t>Пятёрочка / Купер</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="inlineStr">
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="18" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B47" s="19" t="inlineStr">
         <is>
           <t>H78873793353</t>
         </is>
       </c>
-      <c r="C35" s="10" t="inlineStr">
+      <c r="C47" s="11" t="inlineStr">
         <is>
           <t>Кетчуп Махеевъ Томатный 300 г</t>
         </is>
       </c>
-      <c r="D35" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="11" t="n">
+      <c r="D47" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="21" t="n">
         <v>94.98999999999999</v>
       </c>
-      <c r="F35" s="11" t="n">
+      <c r="F47" s="22" t="n">
         <v>94.98999999999999</v>
       </c>
-      <c r="G35" s="10" t="inlineStr">
+      <c r="G47" s="11" t="inlineStr">
         <is>
           <t>Пятёрочка / Купер</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B36" s="15" t="inlineStr">
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="13" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
         <is>
           <t>H35368078464</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>Кетчуп Махеевъ Томатный 300 г</t>
         </is>
       </c>
-      <c r="D36" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" s="9" t="n">
+      <c r="D48" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="16" t="n">
         <v>99.98999999999999</v>
       </c>
-      <c r="F36" s="9" t="n">
+      <c r="F48" s="17" t="n">
         <v>99.98999999999999</v>
       </c>
-      <c r="G36" s="8" t="inlineStr">
+      <c r="G48" s="8" t="inlineStr">
         <is>
           <t>Пятёрочка / Купер</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="inlineStr">
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="18" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B49" s="19" t="inlineStr">
         <is>
           <t>H97269082721</t>
         </is>
       </c>
-      <c r="C37" s="10" t="inlineStr">
+      <c r="C49" s="11" t="inlineStr">
         <is>
           <t>Аджика Амца Абхазская классическая 200 г</t>
         </is>
       </c>
-      <c r="D37" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="11" t="n">
+      <c r="D49" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="21" t="n">
         <v>239.99</v>
       </c>
-      <c r="F37" s="11" t="n">
+      <c r="F49" s="22" t="n">
         <v>239.99</v>
       </c>
-      <c r="G37" s="10" t="inlineStr">
+      <c r="G49" s="11" t="inlineStr">
         <is>
           <t>Пятёрочка / Купер</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B38" s="15" t="inlineStr">
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="13" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
         <is>
           <t>H46634869050</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
         <is>
           <t>Зубная паста Biorepair Total Protective Repair 75 мл</t>
         </is>
       </c>
-      <c r="D38" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="9" t="n">
+      <c r="D50" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="16" t="n">
         <v>739.9</v>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F50" s="17" t="n">
         <v>739.9</v>
       </c>
-      <c r="G38" s="8" t="inlineStr">
+      <c r="G50" s="8" t="inlineStr">
         <is>
           <t>SPAR / Купер</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="inlineStr">
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="18" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B51" s="19" t="inlineStr">
         <is>
           <t>H97269082721</t>
         </is>
       </c>
-      <c r="C39" s="10" t="inlineStr">
+      <c r="C51" s="11" t="inlineStr">
         <is>
           <t>Кетчуп Махеевъ Томатный 300 г</t>
         </is>
       </c>
-      <c r="D39" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="11" t="n">
+      <c r="D51" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="21" t="n">
         <v>84.98999999999999</v>
       </c>
-      <c r="F39" s="11" t="n">
+      <c r="F51" s="22" t="n">
         <v>84.98999999999999</v>
       </c>
-      <c r="G39" s="10" t="inlineStr">
+      <c r="G51" s="11" t="inlineStr">
         <is>
           <t>Пятёрочка / Купер</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="8" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="B40" s="15" t="inlineStr">
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="13" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B52" s="14" t="inlineStr">
         <is>
           <t>H81066596434</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>Зубная паста Biorepair Active shield 75 мл</t>
         </is>
       </c>
-      <c r="D40" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" s="9" t="n">
+      <c r="D52" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" s="16" t="n">
         <v>759.99</v>
       </c>
-      <c r="F40" s="9" t="n">
+      <c r="F52" s="17" t="n">
         <v>759.99</v>
       </c>
-      <c r="G40" s="8" t="inlineStr">
+      <c r="G52" s="8" t="inlineStr">
         <is>
           <t>Перекрёсток / Купер</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="B41" s="16" t="inlineStr">
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="18" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B53" s="19" t="inlineStr">
         <is>
           <t>H81066596434</t>
         </is>
       </c>
-      <c r="C41" s="10" t="inlineStr">
+      <c r="C53" s="11" t="inlineStr">
         <is>
           <t>Кетчуп Махеевъ Шашлычный 500 г</t>
         </is>
       </c>
-      <c r="D41" s="10" t="n">
+      <c r="D53" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="E41" s="11" t="n">
+      <c r="E53" s="21" t="n">
         <v>129.49</v>
       </c>
-      <c r="F41" s="11" t="n">
+      <c r="F53" s="22" t="n">
         <v>258.98</v>
       </c>
-      <c r="G41" s="10" t="inlineStr">
+      <c r="G53" s="11" t="inlineStr">
         <is>
           <t>Перекрёсток / Купер</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="12" t="n"/>
-      <c r="C42" s="13" t="inlineStr">
+    <row r="54" ht="24" customHeight="1">
+      <c r="A54" s="23" t="inlineStr"/>
+      <c r="B54" s="24" t="inlineStr"/>
+      <c r="C54" s="23" t="inlineStr">
         <is>
           <t>Итого к перевыставлению</t>
         </is>
       </c>
-      <c r="D42" s="12" t="n"/>
-      <c r="E42" s="12" t="n"/>
-      <c r="F42" s="14" t="n">
+      <c r="D54" s="24" t="inlineStr"/>
+      <c r="E54" s="24" t="inlineStr"/>
+      <c r="F54" s="25" t="n">
         <v>9853.559999999999</v>
       </c>
-      <c r="G42" s="12" t="n"/>
+      <c r="G54" s="23" t="inlineStr">
+        <is>
+          <t>40 позиций</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F22"/>
+  <autoFilter ref="A13:G53"/>
+  <mergeCells count="9">
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B6:D6"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1824,62 +2025,115 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>Что перевыставляем Фурику</t>
-        </is>
-      </c>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ПРАВИЛА ПЕРЕВЫСТАВЛЕНИЯ</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Оформление как у договора ремонта (пастель: жёлтый / крем, текст чёрный)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Правило</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Включать: зубные пасты, аджики, кетчупы, соусы, освежители воздуха, средства для стирки/гель, леденцы/конфеты Halls (+ иное по указанию).</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Не включать (кофейня): апельсины, грейпфрут, лайм, лимоны, салфетки, вода, мята, перчатки, тоники Rich, мёд, корица и пр. товар точки.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Пример исключения: METRO 08.06.2026 — всё в кофейню, на Фурика 0 ₽.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Не включать сборку/доставку/сервисный сбор, пока не сказано иное.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Дата = дата на карточке заказа в Купере (на скрине).</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>Стоимость = цена за 1 шт; Сумма = стоимость × количество.</t>
         </is>
       </c>
     </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>Итого к перевыставлению: 9 853,56 ₽ · 40 позиций,</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="n"/>
+    </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A12:B12"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>